--- a/examples/demos/04_reverse_stress_test.xlsx
+++ b/examples/demos/04_reverse_stress_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9A3CF1-BB99-436A-A19F-D28A3D4FD1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3833C524-3B82-47AB-AD09-04ACC587AF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Demo 04 — Reverse stress test: what makes the budget break</t>
   </si>
@@ -54,33 +54,45 @@
     <t>Tools demonstrated: replace_constant_with_distribution, wrap_with_output, run_simulation, get_simulation_results, reverse_stress_test</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/04_reverse_stress_test.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 04_reverse_stress_test.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  In the Model sheet of this workbook, replace each base cost in B6:B13 with the matching distribution from column D, using the WBS line names as input names; wrap Total cost B15 as output "TotalCost"; run 5,000 iterations. Then report the chance the total exceeds the 10,500 budget and the P90 total, and run a reverse stress test: when TotalCost breaches 10,500, which inputs drive it and what does the typical breach scenario look like?</t>
+  </si>
+  <si>
+    <t>Expected: the forward risk view plus the breach-driver ranking and a named stress scenario.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Open the workbook and look at the Model sheet: 8 WBS lines with base costs (blue inputs) and suggested distributions in column D.</t>
   </si>
   <si>
+    <t>PROMPT →  Open 04_reverse_stress_test.xlsx from the demo folder.</t>
+  </si>
+  <si>
     <t>Expected: the workbook opens; Model!B15 shows a deterministic total of 9,750 $k and B17 shows 750 $k headroom.</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Make it probabilistic in one shot.</t>
   </si>
   <si>
@@ -90,9 +102,6 @@
     <t>Expected: B6:B13 become VoseInput-wrapped PERT formulas, B15 becomes output "TotalCost", and a 5,000-iteration simulation completes.</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Forward view first: how bad is it, looking forwards?</t>
   </si>
   <si>
@@ -102,9 +111,6 @@
     <t>Expected: a breach probability (roughly 10-25%) and a P90 total somewhat above the 10,500 budget.</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Now the reverse stress test: condition on the bad outcomes and ask what caused them.</t>
   </si>
   <si>
@@ -112,9 +118,6 @@
   </si>
   <si>
     <t>Expected: a breach-driver ranking — each input’s shift in its own SDs inside the breach set — plus a named mean-input-vector stress scenario (reverse_stress_test).</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>Vary the question: define the breach relatively instead of by the fixed budget.</t>
@@ -244,7 +247,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +279,51 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -298,18 +346,38 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -354,39 +422,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +766,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -700,220 +774,247 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="22"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="20"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="18"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="16" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="17"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="18"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="18"/>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="13">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
+    <row r="22" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="13">
+        <v>2</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
+    <row r="26" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3" t="s">
+    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="13">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
+    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="13">
+        <v>4</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3" t="s">
+    <row r="34" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
+    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="13">
+        <v>5</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
+    <row r="38" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="16" t="s">
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="17"/>
-    </row>
-    <row r="36" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="4" t="s">
+    </row>
+    <row r="41" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
+      <c r="B41" s="18"/>
+    </row>
+    <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="4" t="s">
+    <row r="43" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="4" t="s">
+    <row r="44" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="16" t="s">
+    <row r="45" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="17"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="5"/>
-      <c r="B42" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" s="6"/>
-      <c r="B43" s="1" t="s">
+      <c r="B47" s="18"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="14"/>
+      <c r="B48" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A44" s="7"/>
-      <c r="B44" s="1" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="15"/>
+      <c r="B49" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="2"/>
-      <c r="B45" s="1" t="s">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A50" s="16"/>
+      <c r="B50" s="10" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="11"/>
+      <c r="B51" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A14:B14"/>
+  <mergeCells count="8">
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -934,159 +1035,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="A1" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
+      <c r="A4" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="5">
         <v>950</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>47</v>
+      <c r="D6" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5">
         <v>2400</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>49</v>
+      <c r="D7" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5">
         <v>1900</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>51</v>
+      <c r="D8" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5">
         <v>1450</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>53</v>
+      <c r="D9" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="5">
         <v>1200</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>55</v>
+      <c r="D10" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="11">
+      <c r="A11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="5">
         <v>600</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>57</v>
+      <c r="D11" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="11">
+      <c r="A12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="5">
         <v>800</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>59</v>
+      <c r="D12" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="11">
+      <c r="A13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="5">
         <v>450</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>61</v>
+      <c r="D13" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="A15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8">
         <f>SUM(B6:B13)</f>
         <v>9750</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>63</v>
+      <c r="D15" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="5">
         <v>10500</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="9">
         <f>B16-B15</f>
         <v>750</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>66</v>
+      <c r="D17" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demos/04_reverse_stress_test.xlsx
+++ b/examples/demos/04_reverse_stress_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3833C524-3B82-47AB-AD09-04ACC587AF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C958D-0FCA-41EE-8998-2F537667947D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,12 +450,12 @@
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -774,16 +774,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="22"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="17" t="s">
@@ -1038,25 +1038,25 @@
       <c r="A1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="1:4" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">

--- a/examples/demos/04_reverse_stress_test.xlsx
+++ b/examples/demos/04_reverse_stress_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C958D-0FCA-41EE-8998-2F537667947D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404A8EE4-2F1C-4485-8355-FEEB2559D82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
